--- a/public/assets/images/sample.xlsx
+++ b/public/assets/images/sample.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
-  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="132" yWindow="576" windowWidth="18876" windowHeight="8676"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
+    <sheet name="Worksheet" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="144525" forceFullCalc="1"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="31">
   <si>
     <t>Student Name</t>
   </si>
@@ -80,20 +81,55 @@
   </si>
   <si>
     <t>UK</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Boy</t>
+  </si>
+  <si>
+    <t>Girl</t>
+  </si>
+  <si>
+    <t>SEN</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>G&amp;T</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Citizen</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
-      <b/>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -141,19 +177,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="2" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -443,15 +474,23 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:N3"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="4" max="4" width="27.21875" customWidth="1"/>
-    <col min="5" max="5" width="59" customWidth="1"/>
+    <col min="4" max="4" width="27.21875" customWidth="true" style="0"/>
+    <col min="5" max="5" width="59" customWidth="true" style="0"/>
+    <col min="10" max="10" width="9.10" style="0"/>
+    <col min="11" max="11" width="10" customWidth="true" style="0"/>
+    <col min="12" max="12" width="10" customWidth="true" style="0"/>
+    <col min="13" max="13" width="10" customWidth="true" style="0"/>
+    <col min="14" max="14" width="10" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -482,8 +521,20 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -514,8 +565,20 @@
       <c r="J2" t="s">
         <v>16</v>
       </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>26</v>
+      </c>
+      <c r="M2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" t="s">
+        <v>29</v>
+      </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -546,8 +609,31 @@
       <c r="J3" t="s">
         <v>16</v>
       </c>
+      <c r="K3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L3" t="s">
+        <v>27</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>27</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>